--- a/contenus/tab2/exs5-si-imbriques.xlsx
+++ b/contenus/tab2/exs5-si-imbriques.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consignes" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercice" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Correction" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -976,350 +975,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Référence</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Désignation</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Quantité en stock</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Seuil critique</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Seuil d'alerte</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Statut</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>REF601</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Casque de chantier</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E2" t="n">
-        <v>20</v>
-      </c>
-      <c r="F2">
-        <f>IF(C2&lt;=D2,"Urgent",IF(C2&lt;=E2,"À commander","OK"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>REF602</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Gants de manutention</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>15</v>
-      </c>
-      <c r="D3" t="n">
-        <v>10</v>
-      </c>
-      <c r="E3" t="n">
-        <v>20</v>
-      </c>
-      <c r="F3">
-        <f>IF(C3&lt;=D3,"Urgent",IF(C3&lt;=E3,"À commander","OK"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>REF603</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Chaussures de sécurité</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>30</v>
-      </c>
-      <c r="D4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F4">
-        <f>IF(C4&lt;=D4,"Urgent",IF(C4&lt;=E4,"À commander","OK"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>REF604</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Gilet haute visibilité</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>8</v>
-      </c>
-      <c r="D5" t="n">
-        <v>5</v>
-      </c>
-      <c r="E5" t="n">
-        <v>15</v>
-      </c>
-      <c r="F5">
-        <f>IF(C5&lt;=D5,"Urgent",IF(C5&lt;=E5,"À commander","OK"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>REF605</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Lunettes de protection</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" t="n">
-        <v>15</v>
-      </c>
-      <c r="F6">
-        <f>IF(C6&lt;=D6,"Urgent",IF(C6&lt;=E6,"À commander","OK"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>REF606</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Bouchons d'oreille</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>50</v>
-      </c>
-      <c r="D7" t="n">
-        <v>20</v>
-      </c>
-      <c r="E7" t="n">
-        <v>40</v>
-      </c>
-      <c r="F7">
-        <f>IF(C7&lt;=D7,"Urgent",IF(C7&lt;=E7,"À commander","OK"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>REF607</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Diable pliant</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>20</v>
-      </c>
-      <c r="D8" t="n">
-        <v>20</v>
-      </c>
-      <c r="E8" t="n">
-        <v>40</v>
-      </c>
-      <c r="F8">
-        <f>IF(C8&lt;=D8,"Urgent",IF(C8&lt;=E8,"À commander","OK"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>REF608</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Transpalette manuel</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>40</v>
-      </c>
-      <c r="D9" t="n">
-        <v>20</v>
-      </c>
-      <c r="E9" t="n">
-        <v>40</v>
-      </c>
-      <c r="F9">
-        <f>IF(C9&lt;=D9,"Urgent",IF(C9&lt;=E9,"À commander","OK"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>REF609</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Rouleau de film étirable</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>12</v>
-      </c>
-      <c r="D10" t="n">
-        <v>8</v>
-      </c>
-      <c r="E10" t="n">
-        <v>18</v>
-      </c>
-      <c r="F10">
-        <f>IF(C10&lt;=D10,"Urgent",IF(C10&lt;=E10,"À commander","OK"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>REF610</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Carton d'emballage</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>6</v>
-      </c>
-      <c r="D11" t="n">
-        <v>8</v>
-      </c>
-      <c r="E11" t="n">
-        <v>18</v>
-      </c>
-      <c r="F11">
-        <f>IF(C11&lt;=D11,"Urgent",IF(C11&lt;=E11,"À commander","OK"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>REF611</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Étiquettes code-barres</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>100</v>
-      </c>
-      <c r="D12" t="n">
-        <v>50</v>
-      </c>
-      <c r="E12" t="n">
-        <v>80</v>
-      </c>
-      <c r="F12">
-        <f>IF(C12&lt;=D12,"Urgent",IF(C12&lt;=E12,"À commander","OK"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>REF612</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Sangle d'arrimage</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>80</v>
-      </c>
-      <c r="D13" t="n">
-        <v>50</v>
-      </c>
-      <c r="E13" t="n">
-        <v>80</v>
-      </c>
-      <c r="F13">
-        <f>IF(C13&lt;=D13,"Urgent",IF(C13&lt;=E13,"À commander","OK"))</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>